--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
@@ -565,67 +565,67 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0854</v>
+        <v>10.4395</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8101</v>
+        <v>10.6253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2753000000000001</v>
+        <v>-0.1859000000000002</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8673</v>
+        <v>2.0469</v>
       </c>
       <c r="H2" t="n">
-        <v>1.506</v>
+        <v>1.5589</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3612000000000002</v>
+        <v>0.488</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1817</v>
+        <v>7.6342</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4915</v>
+        <v>4.7319</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6903</v>
+        <v>2.9023</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.3144</v>
+        <v>-5.5873</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.9853</v>
+        <v>-3.173</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3288</v>
+        <v>-2.4143</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.4581</v>
+        <v>-2.4295</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9.2181</v>
+        <v>-9.1104</v>
       </c>
       <c r="R2" t="n">
-        <v>6.76</v>
+        <v>6.6809</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.4969</v>
+        <v>-3.4733</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.2889</v>
+        <v>-3.1847</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2079</v>
+        <v>-0.2886</v>
       </c>
       <c r="V2" t="n">
-        <v>14.1733</v>
+        <v>14.2953</v>
       </c>
       <c r="W2" t="n">
-        <v>15.1355</v>
+        <v>15.2861</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9624</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>10.0482</v>
+        <v>9.967499999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>13.4551</v>
+        <v>13.7576</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4069</v>
+        <v>-3.79</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5092</v>
+        <v>2.4942</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6868</v>
+        <v>5.7302</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.1776</v>
+        <v>-3.2361</v>
       </c>
       <c r="J3" t="n">
-        <v>9.062200000000001</v>
+        <v>9.263400000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>9.284800000000001</v>
+        <v>9.478400000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2226</v>
+        <v>-0.215</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.5531</v>
+        <v>-6.7692</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.5981</v>
+        <v>-3.7481</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.955</v>
+        <v>-3.021</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4823</v>
+        <v>3.4418</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0726</v>
+        <v>-3.0369</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5552</v>
+        <v>6.4784</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7034</v>
+        <v>5.6851</v>
       </c>
       <c r="T3" t="n">
-        <v>5.907</v>
+        <v>5.9321</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2034</v>
+        <v>-0.2470000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.647</v>
+        <v>-1.6534</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5585</v>
+        <v>1.5988</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2055</v>
+        <v>-3.2522</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9.960599999999999</v>
+        <v>9.8111</v>
       </c>
       <c r="E4" t="n">
-        <v>9.624700000000001</v>
+        <v>9.8621</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3358999999999996</v>
+        <v>-0.05100000000000016</v>
       </c>
       <c r="G4" t="n">
-        <v>8.920200000000001</v>
+        <v>8.886900000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>7.414300000000001</v>
+        <v>7.4128</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5059</v>
+        <v>1.4741</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4747</v>
+        <v>7.5887</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8029</v>
+        <v>6.9129</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6718000000000001</v>
+        <v>0.6758</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4456</v>
+        <v>1.2982</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6115</v>
+        <v>0.4998999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8343</v>
+        <v>0.7983</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4096</v>
+        <v>-0.405</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6872</v>
+        <v>-3.6442</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2775</v>
+        <v>3.2393</v>
       </c>
       <c r="S4" t="n">
-        <v>6.2907</v>
+        <v>6.2089</v>
       </c>
       <c r="T4" t="n">
-        <v>4.8395</v>
+        <v>4.8492</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4512</v>
+        <v>1.3596</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.8405</v>
+        <v>-4.8797</v>
       </c>
       <c r="W4" t="n">
-        <v>0.998</v>
+        <v>1.0681</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.8384</v>
+        <v>-5.9481</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6.533199999999999</v>
+        <v>6.511</v>
       </c>
       <c r="E5" t="n">
-        <v>8.395099999999999</v>
+        <v>8.679500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8618</v>
+        <v>-2.1684</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9503</v>
+        <v>1.9638</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8006</v>
+        <v>1.7988</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1496</v>
+        <v>0.1648000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2462</v>
+        <v>4.417199999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0252</v>
+        <v>2.1296</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2209</v>
+        <v>2.2878</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2958</v>
+        <v>-2.4537</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2247</v>
+        <v>-0.3305</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0712</v>
+        <v>-2.1229</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3018</v>
+        <v>4.2515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>5.326</v>
+        <v>5.2638</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1911</v>
+        <v>-0.1803000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3148</v>
+        <v>0.3559000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.506</v>
+        <v>-0.5361</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4721999999999997</v>
+        <v>0.4761000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>4.8583</v>
+        <v>4.9185</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.3861</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2128</v>
+        <v>4.1539</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4075</v>
+        <v>3.5456</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8052000000000001</v>
+        <v>0.6082999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1872</v>
+        <v>4.1509</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1738</v>
+        <v>2.1555</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0133</v>
+        <v>1.9954</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4086</v>
+        <v>4.492500000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7885</v>
+        <v>2.8625</v>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2214</v>
+        <v>-0.3416000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6146000000000003</v>
+        <v>-0.7070000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3932999999999999</v>
+        <v>0.3654000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6387</v>
+        <v>-1.6197</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2775</v>
+        <v>3.2393</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1289</v>
+        <v>-1.1146</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3957000000000001</v>
+        <v>0.4218999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5247</v>
+        <v>-1.5365</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4842</v>
+        <v>-0.5018</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2178</v>
+        <v>1.3226</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6483</v>
+        <v>-3.172</v>
       </c>
       <c r="F7" t="n">
-        <v>4.866099999999999</v>
+        <v>4.4946</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6319</v>
+        <v>2.7232</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4523</v>
+        <v>-1.4623</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0843</v>
+        <v>4.1855</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5855</v>
+        <v>3.868200000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7813</v>
+        <v>-0.6585</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3668</v>
+        <v>4.5268</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9536</v>
+        <v>-1.1449</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.671</v>
+        <v>-0.8037</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2825</v>
+        <v>-0.3411999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8193999999999999</v>
+        <v>-0.8097999999999996</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.7842</v>
+        <v>-7.693200000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>6.9648</v>
+        <v>6.8834</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1117</v>
+        <v>-2.0994</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.0528</v>
+        <v>-1.9786</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.05899999999999994</v>
+        <v>-0.121</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5169</v>
+        <v>1.5086</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0864</v>
+        <v>-1.1227</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4491999999999999</v>
+        <v>0.3868</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1368</v>
+        <v>2.2307</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6877</v>
+        <v>-1.8438</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3005</v>
+        <v>-2.3463</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5653</v>
+        <v>0.5351999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8658</v>
+        <v>-2.8815</v>
       </c>
       <c r="J8" t="n">
-        <v>1.257</v>
+        <v>1.307</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8207</v>
+        <v>1.8563</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5636</v>
+        <v>-0.5493</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5575</v>
+        <v>-3.6533</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2553</v>
+        <v>-1.3211</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3022</v>
+        <v>-2.3322</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4592</v>
+        <v>0.4577</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3957</v>
+        <v>0.4218</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0635</v>
+        <v>0.0358</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4842</v>
+        <v>0.5018</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6171</v>
+        <v>-2.625200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.430800000000001</v>
+        <v>-3.1277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8135999999999999</v>
+        <v>0.5023</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8306000000000001</v>
+        <v>0.8303000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8307</v>
+        <v>0.8302</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001000000000001</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4312</v>
+        <v>0.5862999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0554</v>
+        <v>1.1609</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6240999999999999</v>
+        <v>-0.5746000000000002</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3994999999999999</v>
+        <v>0.2439999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2247</v>
+        <v>-0.3306999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6242000000000001</v>
+        <v>0.5745</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2049</v>
+        <v>-0.2024</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.5308</v>
+        <v>-5.4663</v>
       </c>
       <c r="R9" t="n">
-        <v>5.326</v>
+        <v>5.2638</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4036999999999999</v>
+        <v>-0.3836000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7008000000000001</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1044</v>
+        <v>-1.1322</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8394</v>
+        <v>-2.8694</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9682000000000001</v>
+        <v>1.0038</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8076</v>
+        <v>-3.8731</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2208</v>
+        <v>-3.2289</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2076</v>
+        <v>-4.0651</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9869</v>
+        <v>0.8361999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.932</v>
+        <v>-1.9245</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2185</v>
+        <v>-1.244</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7135</v>
+        <v>-0.6805000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6324</v>
+        <v>-1.5438</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2453</v>
+        <v>-1.2078</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3870999999999998</v>
+        <v>-0.3359999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2996</v>
+        <v>-0.3807</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02689999999999998</v>
+        <v>-0.03630000000000005</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3264</v>
+        <v>-0.3444000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4581</v>
+        <v>2.4295</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2142999999999999</v>
+        <v>-0.2073</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2312</v>
+        <v>0.2523</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4456</v>
+        <v>-0.4596</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0745</v>
+        <v>-1.0969</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7262000000000001</v>
+        <v>-0.7527999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.112299999999999</v>
+        <v>-8.2067</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5641</v>
+        <v>-5.3504</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5482</v>
+        <v>-2.8564</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.486800000000001</v>
+        <v>-7.543699999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.753699999999999</v>
+        <v>-4.838699999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.733</v>
+        <v>-2.7051</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.396700000000001</v>
+        <v>-4.2684</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8282</v>
+        <v>-2.7704</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5685</v>
+        <v>-1.4979</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.09</v>
+        <v>-3.2755</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9255</v>
+        <v>-2.0683</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1645</v>
+        <v>-1.2072</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.229</v>
+        <v>-1.2148</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2775</v>
+        <v>3.2393</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0093</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4224</v>
+        <v>-0.3692</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.587</v>
+        <v>-0.6263000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1488</v>
+        <v>-2.194</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7254</v>
+        <v>-11.6099</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.434799999999999</v>
+        <v>-8.084099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2903</v>
+        <v>-3.5257</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.553599999999999</v>
+        <v>-8.536200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.945</v>
+        <v>-4.9608</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.6085</v>
+        <v>-3.5754</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.5036</v>
+        <v>-4.355600000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.71</v>
+        <v>-1.6252</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7934</v>
+        <v>-2.7303</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.05</v>
+        <v>-4.1805</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.2348</v>
+        <v>-3.3355</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8151000000000002</v>
+        <v>-0.8451000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.5067</v>
+        <v>-4.4539</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.3745</v>
+        <v>-7.2883</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6612</v>
+        <v>-2.6279</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0054</v>
+        <v>-1.954</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6558999999999999</v>
+        <v>-0.6739999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9962</v>
+        <v>4.008</v>
       </c>
       <c r="W12" t="n">
-        <v>5.448600000000001</v>
+        <v>5.513599999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4524</v>
+        <v>-1.5056</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.7281</v>
+        <v>-12.8661</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.7524</v>
+        <v>-9.433</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9757</v>
+        <v>-3.433</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.6073</v>
+        <v>-8.611699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.334</v>
+        <v>0.2983000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.9412</v>
+        <v>-8.9101</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.4187</v>
+        <v>-5.2121</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1481</v>
+        <v>2.2672</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.566800000000001</v>
+        <v>-7.4792</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1887</v>
+        <v>-3.3997</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8142</v>
+        <v>-1.9688</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3744</v>
+        <v>-1.4308</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R13" t="n">
-        <v>5.1211</v>
+        <v>5.0614</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6345</v>
+        <v>1.6023</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9128999999999999</v>
+        <v>-0.8401000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5474</v>
+        <v>2.4423</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.8039</v>
+        <v>-7.8811</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.4557</v>
+        <v>-7.5369</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4.103500000000007</v>
+        <v>4.055599999999991</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79129999999999</v>
+        <v>15.4685</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.687600000000002</v>
+        <v>-11.4128</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.983499999999996</v>
+        <v>-5.866199999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>7.942</v>
+        <v>7.814100000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.9252</v>
+        <v>-13.6809</v>
       </c>
       <c r="J14" t="n">
-        <v>21.6957</v>
+        <v>23.7776</v>
       </c>
       <c r="K14" t="n">
-        <v>23.8523</v>
+        <v>25.1378</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.1563</v>
+        <v>-1.359599999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-27.679</v>
+        <v>-29.6442</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.9098</v>
+        <v>-17.3231</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.7683</v>
+        <v>-12.3209</v>
       </c>
       <c r="P14" t="n">
-        <v>7.169300000000001</v>
+        <v>7.086200000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-46.0902</v>
+        <v>-45.5523</v>
       </c>
       <c r="R14" t="n">
-        <v>53.25990000000001</v>
+        <v>52.63809999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.870700000000001</v>
+        <v>2.872100000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>4.102300000000001</v>
+        <v>4.655100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2318</v>
+        <v>-1.783599999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.04649999999999732</v>
+        <v>-0.03549999999999809</v>
       </c>
       <c r="W14" t="n">
-        <v>32.08440000000001</v>
+        <v>32.5864</v>
       </c>
       <c r="X14" t="n">
-        <v>-32.0378</v>
+        <v>-32.6223</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4395</v>
+        <v>13.9604</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6253</v>
+        <v>13.9959</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1859000000000002</v>
+        <v>-0.03549999999999986</v>
       </c>
       <c r="G2" t="n">
         <v>2.0469</v>
@@ -610,13 +610,13 @@
         <v>6.6809</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.4733</v>
+        <v>0.04749999999999988</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.1847</v>
+        <v>0.1858</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2886</v>
+        <v>-0.1383</v>
       </c>
       <c r="V2" t="n">
         <v>14.2953</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.967499999999999</v>
+        <v>8.254199999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>13.7576</v>
+        <v>9.5982</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.79</v>
+        <v>-1.344</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4942</v>
+        <v>1.9638</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7302</v>
+        <v>1.7988</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2361</v>
+        <v>0.1648000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>9.263400000000001</v>
+        <v>4.417199999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>9.478400000000001</v>
+        <v>2.1296</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.215</v>
+        <v>2.2878</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.7692</v>
+        <v>-2.4537</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.7481</v>
+        <v>-0.3305</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.021</v>
+        <v>-2.1229</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4418</v>
+        <v>4.2515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0369</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>6.4784</v>
+        <v>5.2638</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6851</v>
+        <v>1.5628</v>
       </c>
       <c r="T3" t="n">
-        <v>5.9321</v>
+        <v>1.2747</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2470000000000001</v>
+        <v>0.2882</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6534</v>
+        <v>0.4761000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5988</v>
+        <v>4.9185</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2522</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9.8111</v>
+        <v>7.190300000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9.8621</v>
+        <v>10.4442</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05100000000000016</v>
+        <v>-3.2539</v>
       </c>
       <c r="G4" t="n">
-        <v>8.886900000000001</v>
+        <v>2.4942</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4128</v>
+        <v>5.7302</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4741</v>
+        <v>-3.2361</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5887</v>
+        <v>9.263400000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>6.9129</v>
+        <v>9.478400000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6758</v>
+        <v>-0.215</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2982</v>
+        <v>-6.7692</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4998999999999999</v>
+        <v>-3.7481</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7983</v>
+        <v>-3.021</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.405</v>
+        <v>3.4418</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6442</v>
+        <v>-3.0369</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2393</v>
+        <v>6.4784</v>
       </c>
       <c r="S4" t="n">
-        <v>6.2089</v>
+        <v>2.908</v>
       </c>
       <c r="T4" t="n">
-        <v>4.8492</v>
+        <v>2.6188</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3596</v>
+        <v>0.2892</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.8797</v>
+        <v>-1.6534</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0681</v>
+        <v>1.5988</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.9481</v>
+        <v>-3.2522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6.511</v>
+        <v>5.4237</v>
       </c>
       <c r="E5" t="n">
-        <v>8.679500000000001</v>
+        <v>6.2927</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1684</v>
+        <v>-0.8690000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9638</v>
+        <v>8.886900000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7988</v>
+        <v>7.4128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1648000000000001</v>
+        <v>1.4741</v>
       </c>
       <c r="J5" t="n">
-        <v>4.417199999999999</v>
+        <v>7.5887</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1296</v>
+        <v>6.9129</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2878</v>
+        <v>0.6758</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4537</v>
+        <v>1.2982</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3305</v>
+        <v>0.4998999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1229</v>
+        <v>0.7983</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2515</v>
+        <v>-0.405</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0123</v>
+        <v>-3.6442</v>
       </c>
       <c r="R5" t="n">
-        <v>5.2638</v>
+        <v>3.2393</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1803000000000001</v>
+        <v>1.8213</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3559000000000001</v>
+        <v>1.2798</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5361</v>
+        <v>0.5415000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4761000000000001</v>
+        <v>-4.8797</v>
       </c>
       <c r="W5" t="n">
-        <v>4.9185</v>
+        <v>1.0681</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.4424</v>
+        <v>-5.9481</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1539</v>
+        <v>4.4096</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5456</v>
+        <v>3.2827</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6082999999999998</v>
+        <v>1.127</v>
       </c>
       <c r="G6" t="n">
         <v>4.1509</v>
@@ -922,13 +922,13 @@
         <v>3.2393</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1146</v>
+        <v>-0.859</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4218999999999999</v>
+        <v>0.1589</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5365</v>
+        <v>-1.0179</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5018</v>
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3226</v>
+        <v>3.7128</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.172</v>
+        <v>-0.9434</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4946</v>
+        <v>4.6562</v>
       </c>
       <c r="G7" t="n">
         <v>2.7232</v>
@@ -1000,13 +1000,13 @@
         <v>6.8834</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0994</v>
+        <v>0.2906999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9786</v>
+        <v>0.2501</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.121</v>
+        <v>0.04070000000000003</v>
       </c>
       <c r="V7" t="n">
         <v>1.5086</v>
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3868</v>
+        <v>-0.1839000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2307</v>
+        <v>1.8154</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8438</v>
+        <v>-1.9993</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3463</v>
@@ -1078,13 +1078,13 @@
         <v>2.0246</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4577</v>
+        <v>-0.113</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4218</v>
+        <v>0.006600000000000009</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0358</v>
+        <v>-0.1194999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.2509</v>
@@ -1111,13 +1111,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.625200000000001</v>
+        <v>-2.1223</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1277</v>
+        <v>-3.4545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5023</v>
+        <v>1.3324</v>
       </c>
       <c r="G9" t="n">
         <v>0.8303000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>5.2638</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3836000000000001</v>
+        <v>0.1194</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.4215</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1322</v>
+        <v>-0.3021</v>
       </c>
       <c r="V9" t="n">
         <v>-2.8694</v>
@@ -1189,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2289</v>
+        <v>-2.5075</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0651</v>
+        <v>-3.6896</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8361999999999999</v>
+        <v>1.182</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9245</v>
@@ -1234,13 +1234,13 @@
         <v>2.4295</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2073</v>
+        <v>0.5138999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2523</v>
+        <v>0.6278</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4596</v>
+        <v>-0.1139</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0969</v>
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.2067</v>
+        <v>-7.4964</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3504</v>
+        <v>-5.1185</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8564</v>
+        <v>-2.3779</v>
       </c>
       <c r="G11" t="n">
         <v>-7.543699999999999</v>
@@ -1312,13 +1312,13 @@
         <v>3.2393</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.2849999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3692</v>
+        <v>-0.1373000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6263000000000001</v>
+        <v>-0.1477</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6921</v>
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.6099</v>
+        <v>-9.723199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.084099999999999</v>
+        <v>-6.7103</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5257</v>
+        <v>-3.0129</v>
       </c>
       <c r="G12" t="n">
         <v>-8.536200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>2.8344</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6279</v>
+        <v>-0.741</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.954</v>
+        <v>-0.5801999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6739999999999999</v>
+        <v>-0.1609</v>
       </c>
       <c r="V12" t="n">
         <v>4.008</v>
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.8661</v>
+        <v>-12.1728</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.433</v>
+        <v>-8.1233</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.433</v>
+        <v>-4.0495</v>
       </c>
       <c r="G13" t="n">
         <v>-8.611699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>5.0614</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6023</v>
+        <v>2.2956</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8401000000000001</v>
+        <v>0.4697</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4423</v>
+        <v>1.826</v>
       </c>
       <c r="V13" t="n">
         <v>-7.8811</v>
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4.055599999999991</v>
+        <v>8.744899999999989</v>
       </c>
       <c r="E14" t="n">
-        <v>15.4685</v>
+        <v>17.38950000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.4128</v>
+        <v>-8.644399999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-5.866199999999997</v>
@@ -1525,7 +1525,7 @@
         <v>25.1378</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.359599999999999</v>
+        <v>-1.359600000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-29.6442</v>
@@ -1546,19 +1546,19 @@
         <v>52.63809999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.872100000000001</v>
+        <v>7.561199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.655100000000001</v>
+        <v>6.5762</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.783599999999999</v>
+        <v>0.9852999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-0.03549999999999809</v>
       </c>
       <c r="W14" t="n">
-        <v>32.5864</v>
+        <v>32.58639999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-32.6223</v>
